--- a/artfynd/A 48654-2021 artfynd.xlsx
+++ b/artfynd/A 48654-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115188658</v>
+        <v>115328514</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>St. Bråtjärnen, Dls</t>
+          <t>St. Bråtjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316264</v>
+        <v>316412</v>
       </c>
       <c r="R2" t="n">
-        <v>6563679</v>
+        <v>6563485</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,12 +757,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Mossebärljunggranskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -787,7 +778,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Död gran. # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115188446</v>
+        <v>115188658</v>
       </c>
       <c r="B3" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,28 +807,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316324</v>
+        <v>316264</v>
       </c>
       <c r="R3" t="n">
-        <v>6563584</v>
+        <v>6563679</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,7 +883,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,7 +903,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Död gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,15 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115188166</v>
+        <v>115330305</v>
       </c>
       <c r="B4" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,39 +932,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>St. Bråtjärnen, Dls</t>
+          <t>St. Bråtjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316312</v>
+        <v>316321</v>
       </c>
       <c r="R4" t="n">
-        <v>6563583</v>
+        <v>6563549</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,12 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,28 +1008,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Mosseblåbärbarrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1064,12 +1034,7 @@
         <v>115189540</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,15 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115292522</v>
+        <v>115385755</v>
       </c>
       <c r="B6" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,46 +1167,61 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>St. Bråtjärnen S/O., Dls</t>
+          <t>St. Bråtjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>316374</v>
+        <v>316411</v>
       </c>
       <c r="R6" t="n">
-        <v>6563417</v>
+        <v>6563458</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1270,12 +1245,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Utflygande från träd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,28 +1274,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dödt träd. # Picea abies</t>
+          <t>Mosseblåbärblandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1323,62 +1297,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115328436</v>
+        <v>115188166</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>St. Bråtjärnen S., Dls</t>
+          <t>St. Bråtjärnen, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316378</v>
+        <v>316312</v>
       </c>
       <c r="R7" t="n">
-        <v>6563399</v>
+        <v>6563583</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1405,12 +1367,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,6 +1388,21 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Mosseblåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1443,62 +1420,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115034083</v>
+        <v>115188446</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Bråtjärnen S/O, Dls</t>
+          <t>St. Bråtjärnen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316403</v>
+        <v>316324</v>
       </c>
       <c r="R8" t="n">
-        <v>6563384</v>
+        <v>6563584</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1546,6 +1511,21 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Mosseblåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1563,15 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115328293</v>
+        <v>115034083</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1573,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1611,14 +1586,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>St. Bråtjärnen S., Dls</t>
+          <t>Stora Bråtjärnen S/O, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316416</v>
+        <v>316403</v>
       </c>
       <c r="R9" t="n">
-        <v>6563414</v>
+        <v>6563384</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1645,12 +1620,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,7 +1640,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1686,12 +1661,7 @@
         <v>115034110</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1803,42 +1773,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115328514</v>
+        <v>115328293</v>
       </c>
       <c r="B11" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1846,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>316412</v>
+        <v>316416</v>
       </c>
       <c r="R11" t="n">
-        <v>6563485</v>
+        <v>6563414</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1896,22 +1870,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Mossebärljunggranskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Mosseblåbärbarrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1932,12 +1891,7 @@
         <v>115328391</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,77 +1999,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115385755</v>
+        <v>115328436</v>
       </c>
       <c r="B13" t="n">
-        <v>56499</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>St. Bråtjärnen S., Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316411</v>
+        <v>316378</v>
       </c>
       <c r="R13" t="n">
-        <v>6563458</v>
+        <v>6563399</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2142,38 +2079,24 @@
           <t>2024-03-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-03-22</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Utflygande från träd.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Mosseblåbärblandskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 48654-2021 artfynd.xlsx
+++ b/artfynd/A 48654-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115328514</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115188658</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115330305</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115189540</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1294,6 +1319,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115385755</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1417,6 +1447,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115188166</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1540,6 +1575,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115188446</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1655,6 +1695,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115034083</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1770,6 +1815,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115034110</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1885,6 +1935,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115328293</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1996,6 +2051,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115328391</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2111,8 +2171,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115328436</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>